--- a/sample_data/category_task_snapshot/jd_category_snapshot_batch2.xlsx
+++ b/sample_data/category_task_snapshot/jd_category_snapshot_batch2.xlsx
@@ -1,161 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
-  <si>
-    <t>平台</t>
-  </si>
-  <si>
-    <t>月</t>
-  </si>
-  <si>
-    <t>Lv0类目名称(逐月固定)</t>
-  </si>
-  <si>
-    <t>Lv1类目名称(逐月固定)</t>
-  </si>
-  <si>
-    <t>Lv2类目名称(逐月固定)</t>
-  </si>
-  <si>
-    <t>宝贝ID</t>
-  </si>
-  <si>
-    <t>宝贝名称</t>
-  </si>
-  <si>
-    <t>宝贝图片</t>
-  </si>
-  <si>
-    <t>宝贝链接</t>
-  </si>
-  <si>
-    <t>参考价格</t>
-  </si>
-  <si>
-    <t>宝贝品牌(bid)</t>
-  </si>
-  <si>
-    <t>宝贝店铺名称</t>
-  </si>
-  <si>
-    <t>销量</t>
-  </si>
-  <si>
-    <t>销售额</t>
-  </si>
-  <si>
-    <t>价格</t>
-  </si>
-  <si>
-    <t>品牌</t>
-  </si>
-  <si>
-    <t>机型</t>
-  </si>
-  <si>
-    <t>京东</t>
-  </si>
-  <si>
-    <t>家电</t>
-  </si>
-  <si>
-    <t>电脑办公</t>
-  </si>
-  <si>
-    <t>影音娱乐</t>
-  </si>
-  <si>
-    <t>网络设备</t>
-  </si>
-  <si>
-    <t>回音壁</t>
-  </si>
-  <si>
-    <t>路由器</t>
-  </si>
-  <si>
-    <t>sample-sb-003</t>
-  </si>
-  <si>
-    <t>sample-rt-003</t>
-  </si>
-  <si>
-    <t>BOSE Smart Ultra Soundbar 智能回音壁</t>
-  </si>
-  <si>
-    <t>华为 AX3 Pro WiFi6 路由器</t>
-  </si>
-  <si>
-    <t>https://example.com/img/sb003.jpg</t>
-  </si>
-  <si>
-    <t>https://example.com/img/rt003.jpg</t>
-  </si>
-  <si>
-    <t>https://item.jd.com/sample-sb-003.html</t>
-  </si>
-  <si>
-    <t>https://item.jd.com/sample-rt-003.html</t>
-  </si>
-  <si>
-    <t>BOSE</t>
-  </si>
-  <si>
-    <t>华为</t>
-  </si>
-  <si>
-    <t>BOSE官方旗舰店</t>
-  </si>
-  <si>
-    <t>华为京东自营旗舰店</t>
-  </si>
-  <si>
-    <t>HUAWEI</t>
-  </si>
-  <si>
-    <t>Smart Ultra Soundbar</t>
-  </si>
-  <si>
-    <t>AX3 Pro</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -172,21 +51,88 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
-      <protection locked="0"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -474,175 +420,261 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Lv0类目名称(逐月固定)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Lv1类目名称(逐月固定)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Lv2类目名称(逐月固定)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>宝贝ID</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>宝贝名称</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>宝贝图片</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>宝贝链接</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>参考价格</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>宝贝品牌(bid)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>宝贝店铺名称</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>销量</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>价格</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>机型</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>202606</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>家电</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>影音娱乐</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>回音壁</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>sample-sb-003</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>BOSE Smart Ultra Soundbar 智能回音壁</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>https://example.com/img/sb003.jpg</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/sample-sb-003.html</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>6999</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BOSE</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>BOSE官方旗舰店</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="N2" t="n">
+        <v>6999</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6999</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>BOSE</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Smart Ultra Soundbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>202606</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>电脑办公</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>网络设备</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>路由器</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>sample-rt-003</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>华为 AX3 Pro WiFi6 路由器</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>https://example.com/img/rt003.jpg</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>https://item.jd.com/sample-rt-003.html</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>399</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>华为京东自营旗舰店</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
-        <v>202606</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2">
-        <v>6999</v>
-      </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>6999</v>
-      </c>
-      <c r="O2">
-        <v>6999</v>
-      </c>
-      <c r="P2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
-        <v>202606</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3">
+      <c r="N3" t="n">
+        <v>3192</v>
+      </c>
+      <c r="O3" t="n">
         <v>399</v>
       </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3">
-        <v>8</v>
-      </c>
-      <c r="N3">
-        <v>3192</v>
-      </c>
-      <c r="O3">
-        <v>399</v>
-      </c>
-      <c r="P3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>38</v>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>HUAWEI</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>AX3 Pro</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1"/>
-    <hyperlink ref="I2" r:id="rId2"/>
-    <hyperlink ref="H3" r:id="rId3"/>
-    <hyperlink ref="I3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
